--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My2026\Career\projects\PickMe Testing (Manual)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2F65CF-9506-4F02-9CCE-B91F83364C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1729D31-EC01-4650-8D40-B538F318BC8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E9A12C59-D713-4645-977D-ECD6E2730E8D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="242">
   <si>
     <t>TC_ID</t>
   </si>
@@ -501,6 +501,270 @@
   </si>
   <si>
     <t>OTP should not be sent. The user should remain on the same screen. Error message should appear:"Enter a valid registered phone number"</t>
+  </si>
+  <si>
+    <t>TC_30</t>
+  </si>
+  <si>
+    <t>TC_31</t>
+  </si>
+  <si>
+    <t>TC_32</t>
+  </si>
+  <si>
+    <t>TC_33</t>
+  </si>
+  <si>
+    <t>TC_34</t>
+  </si>
+  <si>
+    <t>TC_35</t>
+  </si>
+  <si>
+    <t>TC_36</t>
+  </si>
+  <si>
+    <t>TC_37</t>
+  </si>
+  <si>
+    <t>TC_38</t>
+  </si>
+  <si>
+    <t>TC_39</t>
+  </si>
+  <si>
+    <t>TC_40</t>
+  </si>
+  <si>
+    <t>TC_41</t>
+  </si>
+  <si>
+    <t>TC_42</t>
+  </si>
+  <si>
+    <t>TC_43</t>
+  </si>
+  <si>
+    <t>TC_44</t>
+  </si>
+  <si>
+    <t>TC_45</t>
+  </si>
+  <si>
+    <t>TC_46</t>
+  </si>
+  <si>
+    <t>TC_47</t>
+  </si>
+  <si>
+    <t>TC_48</t>
+  </si>
+  <si>
+    <t>Ride Booking Flow</t>
+  </si>
+  <si>
+    <t>Verify the map correctly fetch the pickup location</t>
+  </si>
+  <si>
+    <t>Verify the map correctly fetch the drop location</t>
+  </si>
+  <si>
+    <t>Verify the different vehicle types appear with price</t>
+  </si>
+  <si>
+    <t>Verify the user can select any vehicle type as his prefer</t>
+  </si>
+  <si>
+    <t>Verify the user can select any payment methods</t>
+  </si>
+  <si>
+    <t>Verify the payment page displays every available payment method and unavailable payment methods</t>
+  </si>
+  <si>
+    <t>Verify the app allows users to add payment methods (add card, add touch)</t>
+  </si>
+  <si>
+    <t>Verify the user is redirected to the ride confirmation screen after selecting vehicle type and payment method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify ETA (estimated arrival time) is displayed correctly for each vehicle type </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify fare updates when changing pickup or drop location </t>
+  </si>
+  <si>
+    <t>Verify app shows “No drivers available” when no vehicles are nearby</t>
+  </si>
+  <si>
+    <t>Verify app allows users to add notes for drivers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify the app allows users to add secondary contact </t>
+  </si>
+  <si>
+    <t>Verify the app allows users to add promo code</t>
+  </si>
+  <si>
+    <t>PickMe app installed. Device network turned on. Location access granted. User has a logged in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PickMe app installed. Device network turned on. Location access granted. User has a logged in. User on the Home page. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify the user is redirected to the pickup and drop location selection screen smoothly </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The user should be navigated to the pickup and drop-off location selection screen smoothly. </t>
+  </si>
+  <si>
+    <t>Pickup: AIA Tower, Srimath Anagarika Dharmapala Mawatha, Colombo</t>
+  </si>
+  <si>
+    <t>Verify the app load the map with pickup and drop location selection prompt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tap on "Rides". Observe the screen behavior. </t>
+  </si>
+  <si>
+    <t>Tap on "Rides". Click on "Your Location" and "Where are you going?". Observe the screen navigation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The map should be load immediately. Pickup and drop-off location selection prompt should display. </t>
+  </si>
+  <si>
+    <t>Tap on "Rides". Click on "Your Location". Enter your Pickup location correctly. Go back to the map.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The screen should load the map immediately. Map should be point-out the pickup location with vehicle moving animation. Pickup location should be preview the correct address on the pickup prompt that entered before. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The screen should load the map immediately. Map should be point-out the drop location with vehicle moving animation. Drop-off location should be preview the correct address on the drop-off prompt that entered before. </t>
+  </si>
+  <si>
+    <t>Tap on "Rides". Click on "Where are you going?". Enter your drop-off location correctly. Go back to the map.</t>
+  </si>
+  <si>
+    <t>Tap on "Rides". Observe the screen pickup and drop location prompt. Observe the map.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pickup and drop-off location prompt should display the your current location as "Your Location". Map should correctly fetch the location. </t>
+  </si>
+  <si>
+    <t>Verify the app fetched the user's current location as the pickup location when the first loanch</t>
+  </si>
+  <si>
+    <t>Tap on "Rides". Enter your pickup location correctly. Enter your drop-off location correctly. Observe the map.</t>
+  </si>
+  <si>
+    <t>Drop: Bus Stand - Colombo   Olcott Mawatha, Pettah, Colombo.</t>
+  </si>
+  <si>
+    <t>Pickup: AIA Tower, Srimath Anagarika Dharmapala Mawatha, Colombo       Drop: Bus Stand - Colombo   Olcott Mawatha, Pettah, Colombo.</t>
+  </si>
+  <si>
+    <t>Tap on "Rides". Enter your pickup location correctly. Enter your drop-off location correctly. Select the any vehicle type. Observe the screen.</t>
+  </si>
+  <si>
+    <t>Tap on "Rides". Enter your pickup location correctly. Enter your drop-off location correctly. Select the vehicle type. Select a payment method. Observe the screen.</t>
+  </si>
+  <si>
+    <t>Pickup: AIA Tower, Srimath Anagarika Dharmapala Mawatha, Colombo       Drop: Bus Stand - Colombo   Olcott Mawatha, Pettah, Colombo.                    Vehicle type: Tuk     Payment method: Cash</t>
+  </si>
+  <si>
+    <t>Tap on "Rides". Enter your pickup location correctly. Enter your drop-off location correctly. Select the vehicle type. Tap on your payment method. Observe the screen.</t>
+  </si>
+  <si>
+    <t>Tap on "Rides". Enter your pickup location correctly. Enter your drop-off location correctly. Select the vehicle type. Tap on your payment method. Tap on '+' mark to add payment method. Observe the screen.</t>
+  </si>
+  <si>
+    <t>Tap on "Rides". Enter your pickup location correctly. Enter your drop-off location correctly. Select the vehicle type. Select a payment method. Click "Book Now" button. Observe the screen.</t>
+  </si>
+  <si>
+    <t>Tap on "Rides". Enter your pickup location correctly. Enter your drop-off location correctly. Select the vehicle type. Select a payment method. Click "Book Now" button. Confirm the booking. Observe the screen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tap on "Rides". Enter your pickup location correctly. Enter your drop-off location correctly. Tap on "Add Note". Enter the message that you want. Click "Done". Observe the app behavior. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tap on "Rides". Enter your pickup location correctly. Enter your drop-off location correctly. Tap on "Add Note". Tap on "Secondary mobile number". Add a number via phone book or create a new contact. Click "Done". Observe the app behavior. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tap on "Rides". Enter your pickup location correctly. Enter your drop-off location correctly. Tap on "Add Promo". Enter the your promo code. Click "Click Add". Observe the app behavior. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The screen should load the map immediately. Map should point-out the pickup and drop-off location and display the route highlighting behind them.  </t>
+  </si>
+  <si>
+    <t>Verify the user redirected to the vehicle type selection after select drop location</t>
+  </si>
+  <si>
+    <t>Tap on "Rides". Enter your pickup and drop-off locations correctly. Observe the screen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The app should display the vehicle selection prompt. </t>
+  </si>
+  <si>
+    <t>Vehicle selection prompt should display the all vehicle types that are available.  Trip fee belongs to each vehicle should display with the vehicle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle selection prompt should display the all available vehicle types with the trip fee. App should allow user to select any vehicle. The selected vehicle should be display as the selected. </t>
+  </si>
+  <si>
+    <t>Pickup: AIA Tower, Srimath Anagarika Dharmapala Mawatha, Colombo       Drop: Bus Stand - Colombo   Olcott Mawatha, Pettah, Colombo.                       Promo Code: *******</t>
+  </si>
+  <si>
+    <t>Pickup: AIA Tower, Srimath Anagarika Dharmapala Mawatha, Colombo       Drop: Bus Stand - Colombo   Olcott Mawatha, Pettah, Colombo.                    Secondary mobile number: (+94) 75 417 2875</t>
+  </si>
+  <si>
+    <t>Pickup: AIA Tower, Srimath Anagarika Dharmapala Mawatha, Colombo       Drop: Bus Stand - Colombo   Olcott Mawatha, Pettah, Colombo.                           Note: I'm standing infront of the AIA tower. Wearing a red t-shirt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pickup: AIA Tower, Srimath Anagarika Dharmapala Mawatha, Colombo       Drop: Bus Stand - Colombo   Olcott Mawatha, Pettah, Colombo.                    Vehicle type: Tuk     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The user should smoothly navigated to the payment method screen and display all payment methods. Available payment methods should be selectable but unavaialable methods should be non-selectable. </t>
+  </si>
+  <si>
+    <t>The user should smoothly navigated to the payment method screen and display all payment methods. Available payment methods should be selectable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The app should open the "Payment" screen. "Add Card" and "Add Touch" options should be displayed to the user. User should be able to add card details and save the card. Validation message should be occure when incorrect card details entering. New payment method should appear in the available payment methods after adding. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">User should be redirected to the ride confirmation screen after the vehicle type and payment method selecting. </t>
+  </si>
+  <si>
+    <t>Tap on "Rides". Enter your pickup location correctly. Enter your drop-off location correctly. Select the vehicle type. Observe the screen.</t>
+  </si>
+  <si>
+    <t>Estimated time for the ride should display with the vehicle type.</t>
+  </si>
+  <si>
+    <t>ETA did not display with the selected vehicle. Vehicle type and price only displayed.</t>
+  </si>
+  <si>
+    <t>If no vehicles are nearby the app should dispplay a message such as "No drivers available". Booking should not be created. No payment should be processed. User should remain on the same screen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add note prompt should display after tapping the "Add Note". User should be abale to type and save the note. The note should be displayed on the confirmation screen. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secondary number adding prompt should displayed after tapping the "Secondary mobile number". User be able to add a number via phone book and create a new contact by manual. Phone book should be open when select the phone book. After adding the new number it should appear under the "Secondary Contact". The number should be saved and displayed on the confirmation screen. Validation messages should occur when adding invalid numbers. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">User should be able to add a promo code. If the code is valid, discount should be apply. If code is invalid error message should appear such as  "Invalid promo code".  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fare should automatically recalculated after the drop or pickup location change. Updated fare should display under each vehicle type instantly. Fare should increase or decrease according to the distance. Old fare should not be remain. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tap on "Rides". Enter your pickup location correctly. Enter your drop-off location correctly. Select the vehicle type. Observe the ride fee. Tap on the drop/pickup location. Change the drop-off/pickup location. Observe the ride fee after location changed. </t>
+  </si>
+  <si>
+    <t>Pickup: AIA Tower, Srimath Anagarika Dharmapala Mawatha, Colombo       Drop: Bus Stand - Colombo   Olcott Mawatha, Pettah, Colombo.                    Vehicle type: Tuk     Updated location: Bambalapitiya.</t>
+  </si>
+  <si>
+    <t>Verify the map correctly displays the route between pickup and drop locations</t>
   </si>
 </sst>
 </file>
@@ -907,7 +1171,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77DD4544-34BE-4E9C-9582-779241C1CD5B}">
-  <dimension ref="A4:I33"/>
+  <dimension ref="A4:I52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" customWidth="1"/>
@@ -1790,6 +2054,557 @@
         <v>12</v>
       </c>
     </row>
+    <row r="34" spans="1:9" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="78" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="109.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="109.2" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="124.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="124.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="109.2" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="171.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="124.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="124.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="140.4" x14ac:dyDescent="0.3">
+      <c r="A48" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="124.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="140.4" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="218.4" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="109.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
